--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -85,19 +85,43 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>SALAZAR</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
   </si>
   <si>
     <t>RONALDO</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
   </si>
   <si>
     <t>LUIS GUILLERMO</t>
@@ -875,7 +899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -907,16 +931,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920147</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -930,16 +954,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920382</v>
+        <v>21330051920147</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -949,6 +973,75 @@
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920340</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920342</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920382</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>SALAZAR</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>PALMA</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
@@ -122,6 +128,9 @@
   </si>
   <si>
     <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>JOCELIN</t>
   </si>
   <si>
     <t>LUIS GUILLERMO</t>
@@ -899,7 +908,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -937,10 +946,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -960,10 +969,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -983,10 +992,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1006,10 +1015,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1023,24 +1032,47 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920382</v>
+        <v>21330051920345</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920382</v>
+      </c>
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
         <v>9</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>13</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -88,52 +88,28 @@
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>CUEVAS</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>CUATRA</t>
   </si>
   <si>
     <t>PALMA</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
     <t>CESAR</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>JOCELIN</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -677,16 +653,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>62.96</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -700,16 +679,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H3">
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -723,16 +705,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>62.5</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -746,16 +731,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>79.17</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -811,16 +799,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>85.19</v>
+        <v>88.89</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -837,16 +825,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>78.95</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -863,16 +851,16 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -889,13 +877,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>83.33</v>
+        <v>87.5</v>
       </c>
       <c r="H5">
         <v>7.4</v>
@@ -908,7 +896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -946,10 +934,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
         <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -963,22 +951,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920147</v>
+        <v>20330051920340</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -986,16 +974,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920340</v>
+        <v>20330051920342</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
         <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1005,75 +993,6 @@
       </c>
       <c r="G4">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920342</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920345</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920382</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -88,28 +88,10 @@
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
     <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
   </si>
 </sst>
 </file>
@@ -653,19 +635,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>62.96</v>
+        <v>92.59</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -705,19 +687,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -799,13 +781,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="H2">
         <v>7.3</v>
@@ -896,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -934,10 +916,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -946,52 +928,6 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920340</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920342</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -88,10 +88,58 @@
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERAS</t>
+  </si>
+  <si>
+    <t>ABAD</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
     <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>CESAR ENRIQUE</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
   </si>
 </sst>
 </file>
@@ -687,16 +735,16 @@
         <v>24</v>
       </c>
       <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
       <c r="F4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H4">
         <v>6.5</v>
@@ -878,7 +926,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -916,10 +964,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -929,6 +977,144 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920341</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920342</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920235</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920331</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920340</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920356</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,63 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
   </si>
 </sst>
 </file>
@@ -592,10 +535,10 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>16</v>
@@ -683,7 +626,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -695,7 +638,7 @@
         <v>92.59</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -709,7 +652,7 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -721,7 +664,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -735,10 +678,10 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>18</v>
@@ -747,7 +690,7 @@
         <v>75</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -761,19 +704,19 @@
         <v>24</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
       <c r="F5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>79.17</v>
+        <v>87.5</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -829,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H2">
         <v>7.3</v>
@@ -855,16 +798,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -878,19 +821,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -907,16 +850,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -956,167 +899,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920145</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920341</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920342</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920235</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920331</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920340</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920356</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
